--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -591,7 +591,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -688,7 +688,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -734,7 +734,7 @@
     <t>Organization.identifier:cliaNum.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_cliaNum</t>
+    <t>http://openelis-global.org/org_cliaNum</t>
   </si>
   <si>
     <t>Organization.identifier:cliaNum.value</t>
@@ -767,7 +767,7 @@
     <t>Organization.identifier:shortName.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_shortName</t>
+    <t>http://openelis-global.org/org_shortName</t>
   </si>
   <si>
     <t>Organization.identifier:shortName.value</t>
@@ -800,7 +800,7 @@
     <t>Organization.identifier:code.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_code</t>
+    <t>http://openelis-global.org/org_code</t>
   </si>
   <si>
     <t>Organization.identifier:code.value</t>
@@ -833,7 +833,7 @@
     <t>Organization.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_uuid</t>
+    <t>http://openelis-global.org/org_uuid</t>
   </si>
   <si>
     <t>Organization.identifier:uuid.value</t>
@@ -903,7 +903,7 @@
     <t>Used to categorize the organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t>Organization.organizationTypes.name</t>
@@ -1400,7 +1400,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1467,7 +1467,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1782,7 +1782,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.74609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1797,7 +1797,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="41.5390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
